--- a/#TikTok_anonymized.xlsx
+++ b/#TikTok_anonymized.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14157,7 +14157,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14200,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14471,7 +14471,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17150,7 +17150,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17360,7 +17360,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20476,7 +20476,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20554,7 +20554,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20593,7 +20593,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20747,7 +20747,7 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20785,7 +20785,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20823,7 +20823,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20861,7 +20861,7 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20899,7 +20899,7 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20975,7 +20975,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21089,7 +21089,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21127,7 +21127,7 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
